--- a/12623168.xlsx
+++ b/12623168.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>Felt good after evening class</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Felt good after first CA</t>
   </si>
 </sst>
 </file>
@@ -3097,24 +3103,50 @@
       </c>
     </row>
     <row r="21" ht="14.6" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" t="str" s="48" cm="1">
+      <c r="A21" s="43">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="44">
+        <v>350</v>
+      </c>
+      <c r="C21" s="44">
+        <v>40</v>
+      </c>
+      <c r="D21" s="44">
+        <v>180</v>
+      </c>
+      <c r="E21" s="44">
+        <v>40</v>
+      </c>
+      <c r="F21" s="44">
+        <v>300</v>
+      </c>
+      <c r="G21" s="44">
+        <v>6</v>
+      </c>
+      <c r="H21" s="44">
+        <v>55</v>
+      </c>
+      <c r="I21" s="45" cm="1">
         <f t="array" ref="I21">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-      </c>
-      <c r="J21" t="str" s="48" cm="1">
+        <v>965</v>
+      </c>
+      <c r="J21" s="45" cm="1">
         <f t="array" ref="J21">IF(I21="","",1440-I21)</f>
-      </c>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
+        <v>475</v>
+      </c>
+      <c r="K21" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L21" t="s" s="46">
+        <v>80</v>
+      </c>
+      <c r="M21" t="s" s="46">
+        <v>65</v>
+      </c>
+      <c r="N21" t="s" s="47">
+        <v>81</v>
+      </c>
     </row>
     <row r="22" ht="14.6" customHeight="1">
       <c r="A22" s="43"/>

--- a/12623168.xlsx
+++ b/12623168.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Felt good after first CA</t>
+  </si>
+  <si>
+    <t>Preparing for CA</t>
   </si>
 </sst>
 </file>
@@ -3149,44 +3152,96 @@
       </c>
     </row>
     <row r="22" ht="14.6" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" t="str" s="48" cm="1">
+      <c r="A22" s="43">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="44">
+        <v>360</v>
+      </c>
+      <c r="C22" s="44">
+        <v>45</v>
+      </c>
+      <c r="D22" s="44">
+        <v>120</v>
+      </c>
+      <c r="E22" s="44">
+        <v>30</v>
+      </c>
+      <c r="F22" s="44">
+        <v>0</v>
+      </c>
+      <c r="G22" s="44">
+        <v>0</v>
+      </c>
+      <c r="H22" s="44">
+        <v>70</v>
+      </c>
+      <c r="I22" s="45" cm="1">
         <f t="array" ref="I22">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-      </c>
-      <c r="J22" t="str" s="48" cm="1">
+        <v>625</v>
+      </c>
+      <c r="J22" s="45" cm="1">
         <f t="array" ref="J22">IF(I22="","",1440-I22)</f>
-      </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
+        <v>815</v>
+      </c>
+      <c r="K22" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L22" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="M22" t="s" s="46">
+        <v>61</v>
+      </c>
+      <c r="N22" t="s" s="47">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" ht="14.6" customHeight="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" t="str" s="48" cm="1">
+      <c r="A23" s="43">
+        <v>46271</v>
+      </c>
+      <c r="B23" s="44">
+        <v>360</v>
+      </c>
+      <c r="C23" s="44">
+        <v>0</v>
+      </c>
+      <c r="D23" s="44">
+        <v>150</v>
+      </c>
+      <c r="E23" s="44">
+        <v>0</v>
+      </c>
+      <c r="F23" s="44">
+        <v>0</v>
+      </c>
+      <c r="G23" s="44">
+        <v>0</v>
+      </c>
+      <c r="H23" s="44">
+        <v>65</v>
+      </c>
+      <c r="I23" s="45" cm="1">
         <f t="array" ref="I23">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-      </c>
-      <c r="J23" t="str" s="48" cm="1">
+        <v>575</v>
+      </c>
+      <c r="J23" s="45" cm="1">
         <f t="array" ref="J23">IF(I23="","",1440-I23)</f>
-      </c>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
+        <v>865</v>
+      </c>
+      <c r="K23" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="L23" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="M23" t="s" s="46">
+        <v>65</v>
+      </c>
+      <c r="N23" t="s" s="47">
+        <v>82</v>
+      </c>
     </row>
     <row r="24" ht="14.6" customHeight="1">
       <c r="A24" s="43"/>

--- a/12623168.xlsx
+++ b/12623168.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Preparing for CA</t>
+  </si>
+  <si>
+    <t>Felt a bit stressed after DBMS CA</t>
   </si>
 </sst>
 </file>
@@ -3244,24 +3247,50 @@
       </c>
     </row>
     <row r="24" ht="14.6" customHeight="1">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" t="str" s="48" cm="1">
+      <c r="A24" s="43">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="44">
+        <v>400</v>
+      </c>
+      <c r="C24" s="44">
+        <v>45</v>
+      </c>
+      <c r="D24" s="44">
+        <v>140</v>
+      </c>
+      <c r="E24" s="44">
+        <v>30</v>
+      </c>
+      <c r="F24" s="44">
+        <v>300</v>
+      </c>
+      <c r="G24" s="44">
+        <v>6</v>
+      </c>
+      <c r="H24" s="44">
+        <v>50</v>
+      </c>
+      <c r="I24" s="45" cm="1">
         <f t="array" ref="I24">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-      </c>
-      <c r="J24" t="str" s="48" cm="1">
+        <v>965</v>
+      </c>
+      <c r="J24" s="45" cm="1">
         <f t="array" ref="J24">IF(I24="","",1440-I24)</f>
-      </c>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
+        <v>475</v>
+      </c>
+      <c r="K24" t="s" s="46">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s" s="46">
+        <v>71</v>
+      </c>
+      <c r="M24" t="s" s="46">
+        <v>61</v>
+      </c>
+      <c r="N24" t="s" s="47">
+        <v>83</v>
+      </c>
     </row>
     <row r="25" ht="14.6" customHeight="1">
       <c r="A25" s="43"/>

--- a/12623168.xlsx
+++ b/12623168.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Felt a bit stressed after DBMS CA</t>
+  </si>
+  <si>
+    <t>Felt good after evening classes</t>
   </si>
 </sst>
 </file>
@@ -3293,44 +3296,96 @@
       </c>
     </row>
     <row r="25" ht="14.6" customHeight="1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" t="str" s="48" cm="1">
+      <c r="A25" s="43">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="44">
+        <v>310</v>
+      </c>
+      <c r="C25" s="44">
+        <v>45</v>
+      </c>
+      <c r="D25" s="44">
+        <v>150</v>
+      </c>
+      <c r="E25" s="44">
+        <v>40</v>
+      </c>
+      <c r="F25" s="44">
+        <v>150</v>
+      </c>
+      <c r="G25" s="44">
+        <v>3</v>
+      </c>
+      <c r="H25" s="44">
+        <v>60</v>
+      </c>
+      <c r="I25" s="45" cm="1">
         <f t="array" ref="I25">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-      </c>
-      <c r="J25" t="str" s="48" cm="1">
+        <v>755</v>
+      </c>
+      <c r="J25" s="45" cm="1">
         <f t="array" ref="J25">IF(I25="","",1440-I25)</f>
-      </c>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
+        <v>685</v>
+      </c>
+      <c r="K25" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L25" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="M25" t="s" s="46">
+        <v>65</v>
+      </c>
+      <c r="N25" t="s" s="47">
+        <v>84</v>
+      </c>
     </row>
     <row r="26" ht="14.6" customHeight="1">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" t="str" s="48" cm="1">
+      <c r="A26" s="43">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="44">
+        <v>340</v>
+      </c>
+      <c r="C26" s="44">
+        <v>50</v>
+      </c>
+      <c r="D26" s="44">
+        <v>180</v>
+      </c>
+      <c r="E26" s="44">
+        <v>35</v>
+      </c>
+      <c r="F26" s="44">
+        <v>400</v>
+      </c>
+      <c r="G26" s="44">
+        <v>8</v>
+      </c>
+      <c r="H26" s="44">
+        <v>75</v>
+      </c>
+      <c r="I26" s="45" cm="1">
         <f t="array" ref="I26">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-      </c>
-      <c r="J26" t="str" s="48" cm="1">
+        <v>1080</v>
+      </c>
+      <c r="J26" s="45" cm="1">
         <f t="array" ref="J26">IF(I26="","",1440-I26)</f>
-      </c>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
+        <v>360</v>
+      </c>
+      <c r="K26" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L26" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="M26" t="s" s="46">
+        <v>61</v>
+      </c>
+      <c r="N26" t="s" s="47">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" ht="14.6" customHeight="1">
       <c r="A27" s="43"/>

--- a/12623168.xlsx
+++ b/12623168.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="86">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Felt good after evening classes</t>
+  </si>
+  <si>
+    <t>Felt good after Freasher's party</t>
   </si>
 </sst>
 </file>
@@ -3388,64 +3391,142 @@
       </c>
     </row>
     <row r="27" ht="14.6" customHeight="1">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" t="str" s="48" cm="1">
+      <c r="A27" s="43">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="44">
+        <v>380</v>
+      </c>
+      <c r="C27" s="44">
+        <v>45</v>
+      </c>
+      <c r="D27" s="44">
+        <v>200</v>
+      </c>
+      <c r="E27" s="44">
+        <v>60</v>
+      </c>
+      <c r="F27" s="44">
+        <v>200</v>
+      </c>
+      <c r="G27" s="44">
+        <v>4</v>
+      </c>
+      <c r="H27" s="44">
+        <v>70</v>
+      </c>
+      <c r="I27" s="45" cm="1">
         <f t="array" ref="I27">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-      </c>
-      <c r="J27" t="str" s="48" cm="1">
+        <v>955</v>
+      </c>
+      <c r="J27" s="45" cm="1">
         <f t="array" ref="J27">IF(I27="","",1440-I27)</f>
-      </c>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
+        <v>485</v>
+      </c>
+      <c r="K27" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L27" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="M27" t="s" s="46">
+        <v>65</v>
+      </c>
+      <c r="N27" t="s" s="47">
+        <v>85</v>
+      </c>
     </row>
     <row r="28" ht="14.6" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" t="str" s="48" cm="1">
+      <c r="A28" s="43">
+        <v>46276</v>
+      </c>
+      <c r="B28" s="44">
+        <v>300</v>
+      </c>
+      <c r="C28" s="44">
+        <v>40</v>
+      </c>
+      <c r="D28" s="44">
+        <v>150</v>
+      </c>
+      <c r="E28" s="44">
+        <v>30</v>
+      </c>
+      <c r="F28" s="44">
+        <v>250</v>
+      </c>
+      <c r="G28" s="44">
+        <v>5</v>
+      </c>
+      <c r="H28" s="44">
+        <v>55</v>
+      </c>
+      <c r="I28" s="45" cm="1">
         <f t="array" ref="I28">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-      </c>
-      <c r="J28" t="str" s="48" cm="1">
+        <v>825</v>
+      </c>
+      <c r="J28" s="45" cm="1">
         <f t="array" ref="J28">IF(I28="","",1440-I28)</f>
-      </c>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
+        <v>615</v>
+      </c>
+      <c r="K28" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="L28" t="s" s="46">
+        <v>71</v>
+      </c>
+      <c r="M28" t="s" s="46">
+        <v>67</v>
+      </c>
+      <c r="N28" t="s" s="47">
+        <v>78</v>
+      </c>
     </row>
     <row r="29" ht="14.6" customHeight="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" t="str" s="48" cm="1">
+      <c r="A29" s="43">
+        <v>46277</v>
+      </c>
+      <c r="B29" s="44">
+        <v>360</v>
+      </c>
+      <c r="C29" s="44">
+        <v>50</v>
+      </c>
+      <c r="D29" s="44">
+        <v>180</v>
+      </c>
+      <c r="E29" s="44">
+        <v>90</v>
+      </c>
+      <c r="F29" s="44">
+        <v>0</v>
+      </c>
+      <c r="G29" s="44">
+        <v>0</v>
+      </c>
+      <c r="H29" s="44">
+        <v>90</v>
+      </c>
+      <c r="I29" s="45" cm="1">
         <f t="array" ref="I29">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-      </c>
-      <c r="J29" t="str" s="48" cm="1">
+        <v>770</v>
+      </c>
+      <c r="J29" s="45" cm="1">
         <f t="array" ref="J29">IF(I29="","",1440-I29)</f>
-      </c>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
+        <v>670</v>
+      </c>
+      <c r="K29" t="s" s="46">
+        <v>59</v>
+      </c>
+      <c r="L29" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="M29" t="s" s="46">
+        <v>65</v>
+      </c>
+      <c r="N29" t="s" s="47">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" ht="14.6" customHeight="1">
       <c r="A30" s="43"/>
